--- a/tabular/core/parvo-ncbi-refseqs-side-data.xlsx
+++ b/tabular/core/parvo-ncbi-refseqs-side-data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr date1904="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/family/Parvovirus-GLUE/tabular/core/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/core/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545E8183-A40F-9F4E-B638-38AAE60C2FB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2ECF2A-7993-5946-87A3-E86515A2E38D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,7 +375,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -519,7 +519,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,24 +702,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF660066"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505021"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,15 +866,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -938,7 +916,152 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF660066"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -949,6 +1072,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0F1BA2E4-5508-D641-A66B-0A885BA8A674}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="13" dataDxfId="0">
+  <autoFilter ref="A1:L24" xr:uid="{C87C2F67-FB52-4C45-9888-A821ECD890CF}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{1886BCFD-3386-054A-A8A2-E81A21CAA57F}" name="sequenceID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{71B0F631-881A-4948-B080-C69E0582F850}" name="virus_name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{ACAD3BB5-B841-0B43-AFFC-6D63DC81311D}" name="virus_full_name" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{7173CCD0-1EF8-AD41-8C4A-89D138C761F6}" name="virus_subfamily" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{510A1728-5FAB-AA4C-A776-FC010971D6E9}" name="virus_genus" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{3C7FF5EA-CA51-0B42-81FC-3020DC95B496}" name="assign_clade" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{6B6AC745-FF47-574D-92B5-73C52C44D505}" name="assign_subclade" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{3D200B96-B2EF-804D-A25A-887C5E15B620}" name="virus_clade_ns" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{239291D0-83A7-2A4D-B34E-5AEC849CA3FA}" name="virus_subclade_ns" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{D488DA1B-26A1-D344-B3EB-9FACCB1BBB69}" name="virus_clade_vp" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{74D61353-4CB9-C141-86B3-0B9F0440579A}" name="virus_subclade_vp" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{963B9AE4-D35C-2742-8869-689EC5EC71BE}" name="host_species" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1249,20 +1393,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="52.83203125" customWidth="1"/>
     <col min="4" max="4" width="28.6640625" customWidth="1"/>
     <col min="5" max="5" width="33.1640625" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="19.33203125" customWidth="1"/>
     <col min="8" max="8" width="16.1640625" customWidth="1"/>
     <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="19.33203125" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
@@ -1300,311 +1447,311 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="F2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
+      <c r="F3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3" t="s">
+      <c r="F4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3" t="s">
+      <c r="F5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3" t="s">
+      <c r="F6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3" t="s">
+      <c r="F7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="3" t="s">
+      <c r="F8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="F9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
@@ -1617,7 +1764,7 @@
       <c r="D10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -1642,7 +1789,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>56</v>
       </c>
@@ -1655,7 +1802,7 @@
       <c r="D11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1680,7 +1827,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -1693,7 +1840,7 @@
       <c r="D12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -1718,7 +1865,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>73</v>
       </c>
@@ -1731,7 +1878,7 @@
       <c r="D13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1756,7 +1903,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
@@ -1769,7 +1916,7 @@
       <c r="D14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -1794,383 +1941,383 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L15" s="4" t="s">
+      <c r="F15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L16" s="4" t="s">
+      <c r="F16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L17" s="4" t="s">
+      <c r="F17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="4" t="s">
+      <c r="F18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="4" t="s">
+      <c r="F20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="4" t="s">
+      <c r="F21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H22" s="4" t="s">
+      <c r="G22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J22" s="4" t="s">
+      <c r="I22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="4" t="s">
+      <c r="L22" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="4" t="s">
+      <c r="F23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L24" s="4" t="s">
+      <c r="F24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2180,15 +2327,18 @@
     <sortCondition ref="E2:E22"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A294D4-B9B4-0343-89CB-D84830908F70}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>65</v>
       </c>
